--- a/data/final.xlsx
+++ b/data/final.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Jun" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Jun Rev" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
@@ -12006,7 +12006,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12035,6 +12035,11 @@
           <t>tickets</t>
         </is>
       </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>items</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
@@ -12054,6 +12059,9 @@
       <c r="E2" t="n">
         <v>6655</v>
       </c>
+      <c r="F2" t="n">
+        <v>9621</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -12073,6 +12081,9 @@
       <c r="E3" t="n">
         <v>5080</v>
       </c>
+      <c r="F3" t="n">
+        <v>7422</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -12092,6 +12103,9 @@
       <c r="E4" t="n">
         <v>4065</v>
       </c>
+      <c r="F4" t="n">
+        <v>5934</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
@@ -12110,6 +12124,9 @@
       </c>
       <c r="E5" t="n">
         <v>5192</v>
+      </c>
+      <c r="F5" t="n">
+        <v>7536</v>
       </c>
     </row>
   </sheetData>

--- a/data/final.xlsx
+++ b/data/final.xlsx
@@ -8,7 +8,7 @@
   </bookViews>
   <sheets>
     <sheet name="Jun Rev" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Summary" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Summary with Items" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
